--- a/Du_lieu_du_bao.xlsx
+++ b/Du_lieu_du_bao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\du_bao_dien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F986E8BD-5371-41FD-86A4-D4FE44CCC74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57694E78-9205-41DB-AE9A-9EC26BBAC403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="14385" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -124,15 +124,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -416,13 +431,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -615,6 +630,38 @@
       </c>
       <c r="J6" s="2">
         <v>440000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="3">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3">
+        <v>75</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1350000</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1450000</v>
+      </c>
+      <c r="H7" s="4">
+        <v>250000</v>
+      </c>
+      <c r="I7" s="4">
+        <v>5250000</v>
+      </c>
+      <c r="J7" s="4">
+        <v>410000</v>
       </c>
     </row>
   </sheetData>
